--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37802-2024 artfynd.xlsx
+++ b/artfynd/A 37802-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439873</v>
       </c>
       <c r="B2" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
